--- a/Table_temp.xlsx
+++ b/Table_temp.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Simulative\АВ_тест\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Simulative\АВ_тест\AB_test_MarketpleteFeed\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="41">
   <si>
     <t>pageviews</t>
   </si>
@@ -114,6 +114,39 @@
   </si>
   <si>
     <t>B-A</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>B+A</t>
+  </si>
+  <si>
+    <t>pageviews_A, %</t>
+  </si>
+  <si>
+    <t>pageviews_В, %</t>
+  </si>
+  <si>
+    <t>revenue_А, %</t>
+  </si>
+  <si>
+    <t>revenue_В, %</t>
+  </si>
+  <si>
+    <t>pageviews_A, % от тотал трафика</t>
+  </si>
+  <si>
+    <t>pageviews_В, % от тотал трафика</t>
+  </si>
+  <si>
+    <t>revenue_А, % от тотал выручки</t>
+  </si>
+  <si>
+    <t>revenue_В, % от тотал выручки</t>
   </si>
 </sst>
 </file>
@@ -125,7 +158,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,13 +192,37 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -212,7 +269,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -235,6 +292,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -517,15 +583,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C5:V33"/>
+  <dimension ref="C5:AB34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="16" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:22" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="C5" s="1"/>
+    <row r="5" spans="3:28" ht="51" x14ac:dyDescent="0.25">
+      <c r="C5" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
@@ -583,8 +653,23 @@
       <c r="V5" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="X5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="6" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>0</v>
       </c>
@@ -645,8 +730,27 @@
       <c r="V6" s="2">
         <v>0.11021499999999999</v>
       </c>
+      <c r="X6" s="5">
+        <v>101</v>
+      </c>
+      <c r="Y6" s="7">
+        <f>F6/SUM($F$6:$F$10)</f>
+        <v>0.18367107772027289</v>
+      </c>
+      <c r="Z6" s="7">
+        <f>O6/SUM($O$6:$O$10)</f>
+        <v>0.18367819897367985</v>
+      </c>
+      <c r="AA6" s="7">
+        <f>I6/SUM($I$6:$I$10)</f>
+        <v>0.21282147408486382</v>
+      </c>
+      <c r="AB6" s="7">
+        <f>R6/SUM($R$6:$R$10)</f>
+        <v>0.20960339641479586</v>
+      </c>
     </row>
-    <row r="7" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1</v>
       </c>
@@ -707,8 +811,27 @@
       <c r="V7" s="2">
         <v>0.104383</v>
       </c>
+      <c r="X7" s="5">
+        <v>106</v>
+      </c>
+      <c r="Y7" s="7">
+        <f>F7/SUM($F$6:$F$10)</f>
+        <v>0.16955264441502335</v>
+      </c>
+      <c r="Z7" s="7">
+        <f>O7/SUM($O$6:$O$10)</f>
+        <v>0.16150471776195993</v>
+      </c>
+      <c r="AA7" s="7">
+        <f>I7/SUM($I$6:$I$10)</f>
+        <v>0.13000505994105477</v>
+      </c>
+      <c r="AB7" s="7">
+        <f>R7/SUM($R$6:$R$10)</f>
+        <v>0.12715930796827463</v>
+      </c>
     </row>
-    <row r="8" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C8" s="1">
         <v>2</v>
       </c>
@@ -769,8 +892,27 @@
       <c r="V8" s="2">
         <v>4.8265000000000002E-2</v>
       </c>
+      <c r="X8" s="5">
+        <v>111</v>
+      </c>
+      <c r="Y8" s="7">
+        <f>F8/SUM($F$6:$F$10)</f>
+        <v>0.14065221935753605</v>
+      </c>
+      <c r="Z8" s="7">
+        <f>O8/SUM($O$6:$O$10)</f>
+        <v>0.14146995530541301</v>
+      </c>
+      <c r="AA8" s="7">
+        <f>I8/SUM($I$6:$I$10)</f>
+        <v>0.49007965176596779</v>
+      </c>
+      <c r="AB8" s="7">
+        <f>R8/SUM($R$6:$R$10)</f>
+        <v>0.48988402953737642</v>
+      </c>
     </row>
-    <row r="9" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C9" s="1">
         <v>3</v>
       </c>
@@ -831,8 +973,27 @@
       <c r="V9" s="2">
         <v>9.4395000000000007E-2</v>
       </c>
+      <c r="X9" s="5">
+        <v>123</v>
+      </c>
+      <c r="Y9" s="7">
+        <f>F9/SUM($F$6:$F$10)</f>
+        <v>0.23473498837584963</v>
+      </c>
+      <c r="Z9" s="7">
+        <f>O9/SUM($O$6:$O$10)</f>
+        <v>0.24098659162390332</v>
+      </c>
+      <c r="AA9" s="7">
+        <f>I9/SUM($I$6:$I$10)</f>
+        <v>7.0634062124769859E-2</v>
+      </c>
+      <c r="AB9" s="7">
+        <f>R9/SUM($R$6:$R$10)</f>
+        <v>7.6748831848028304E-2</v>
+      </c>
     </row>
-    <row r="10" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>4</v>
       </c>
@@ -893,8 +1054,27 @@
       <c r="V10" s="2">
         <v>0.13261100000000001</v>
       </c>
+      <c r="X10" s="5">
+        <v>373</v>
+      </c>
+      <c r="Y10" s="7">
+        <f>F10/SUM($F$6:$F$10)</f>
+        <v>0.27138907013131808</v>
+      </c>
+      <c r="Z10" s="7">
+        <f>O10/SUM($O$6:$O$10)</f>
+        <v>0.27236053633504387</v>
+      </c>
+      <c r="AA10" s="7">
+        <f>I10/SUM($I$6:$I$10)</f>
+        <v>9.64597520833438E-2</v>
+      </c>
+      <c r="AB10" s="7">
+        <f>R10/SUM($R$6:$R$10)</f>
+        <v>9.6604434231524816E-2</v>
+      </c>
     </row>
-    <row r="13" spans="3:22" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:28" ht="25.5" x14ac:dyDescent="0.25">
       <c r="E13" s="9" t="s">
         <v>29</v>
       </c>
@@ -922,8 +1102,35 @@
       <c r="M13" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="O13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="14" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E14" s="5">
         <v>101</v>
       </c>
@@ -959,8 +1166,43 @@
         <f t="shared" si="0"/>
         <v>-5.5996000000000004E-2</v>
       </c>
+      <c r="O14" s="5">
+        <v>101</v>
+      </c>
+      <c r="P14" s="13">
+        <f>F6+O6</f>
+        <v>226938</v>
+      </c>
+      <c r="Q14" s="13">
+        <f t="shared" ref="Q14:T18" si="1">G6+P6</f>
+        <v>70794</v>
+      </c>
+      <c r="R14" s="13">
+        <f t="shared" si="1"/>
+        <v>3820</v>
+      </c>
+      <c r="S14" s="13">
+        <f t="shared" si="1"/>
+        <v>448.60939999999999</v>
+      </c>
+      <c r="T14" s="13">
+        <f>J6+S6</f>
+        <v>9892</v>
+      </c>
+      <c r="U14" s="6">
+        <f>S14/Q14*1000</f>
+        <v>6.3368279797722966</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" ref="V14:V18" si="2">AE6-V6</f>
+        <v>-0.11021499999999999</v>
+      </c>
+      <c r="W14" s="8">
+        <f t="shared" ref="W14:W18" si="3">AF6-W6</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E15" s="5">
         <v>106</v>
       </c>
@@ -996,8 +1238,43 @@
         <f t="shared" si="0"/>
         <v>-0.10369599999999998</v>
       </c>
+      <c r="O15" s="5">
+        <v>106</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15:P18" si="4">F7+O7</f>
+        <v>204628</v>
+      </c>
+      <c r="Q15" s="13">
+        <f t="shared" si="1"/>
+        <v>140834</v>
+      </c>
+      <c r="R15" s="13">
+        <f t="shared" si="1"/>
+        <v>9349</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="1"/>
+        <v>273.11710000000005</v>
+      </c>
+      <c r="T15" s="13">
+        <f t="shared" si="1"/>
+        <v>22448</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" ref="U15:U18" si="5">S15/Q15*1000</f>
+        <v>1.9392838377096442</v>
+      </c>
+      <c r="V15" s="7">
+        <f t="shared" si="2"/>
+        <v>-0.104383</v>
+      </c>
+      <c r="W15" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E16" s="5">
         <v>111</v>
       </c>
@@ -1033,8 +1310,43 @@
         <f t="shared" si="0"/>
         <v>-8.4138999999999992E-2</v>
       </c>
+      <c r="O16" s="5">
+        <v>111</v>
+      </c>
+      <c r="P16" s="13">
+        <f t="shared" si="4"/>
+        <v>174276</v>
+      </c>
+      <c r="Q16" s="13">
+        <f t="shared" si="1"/>
+        <v>70662</v>
+      </c>
+      <c r="R16" s="13">
+        <f t="shared" si="1"/>
+        <v>4859</v>
+      </c>
+      <c r="S16" s="13">
+        <f t="shared" si="1"/>
+        <v>1040.6088999999999</v>
+      </c>
+      <c r="T16" s="13">
+        <f t="shared" si="1"/>
+        <v>6544</v>
+      </c>
+      <c r="U16" s="6">
+        <f t="shared" si="5"/>
+        <v>14.726570150859018</v>
+      </c>
+      <c r="V16" s="7">
+        <f t="shared" si="2"/>
+        <v>-4.8265000000000002E-2</v>
+      </c>
+      <c r="W16" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E17" s="5">
         <v>123</v>
       </c>
@@ -1070,8 +1382,43 @@
         <f t="shared" si="0"/>
         <v>-8.3576999999999985E-2</v>
       </c>
+      <c r="O17" s="5">
+        <v>123</v>
+      </c>
+      <c r="P17" s="13">
+        <f t="shared" si="4"/>
+        <v>293802</v>
+      </c>
+      <c r="Q17" s="13">
+        <f t="shared" si="1"/>
+        <v>47510</v>
+      </c>
+      <c r="R17" s="13">
+        <f t="shared" si="1"/>
+        <v>3630</v>
+      </c>
+      <c r="S17" s="13">
+        <f t="shared" si="1"/>
+        <v>156.42000000000002</v>
+      </c>
+      <c r="T17" s="13">
+        <f t="shared" si="1"/>
+        <v>6535</v>
+      </c>
+      <c r="U17" s="6">
+        <f t="shared" si="5"/>
+        <v>3.2923595032624715</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" si="2"/>
+        <v>-9.4395000000000007E-2</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E18" s="5">
         <v>373</v>
       </c>
@@ -1107,502 +1454,808 @@
         <f t="shared" si="0"/>
         <v>-9.7307000000000005E-2</v>
       </c>
+      <c r="O18" s="5">
+        <v>373</v>
+      </c>
+      <c r="P18" s="13">
+        <f t="shared" si="4"/>
+        <v>335900</v>
+      </c>
+      <c r="Q18" s="13">
+        <f t="shared" si="1"/>
+        <v>84855</v>
+      </c>
+      <c r="R18" s="13">
+        <f t="shared" si="1"/>
+        <v>2249</v>
+      </c>
+      <c r="S18" s="13">
+        <f t="shared" si="1"/>
+        <v>205.0095</v>
+      </c>
+      <c r="T18" s="13">
+        <f t="shared" si="1"/>
+        <v>16069</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" si="5"/>
+        <v>2.4159978787343115</v>
+      </c>
+      <c r="V18" s="7">
+        <f t="shared" si="2"/>
+        <v>-0.13261100000000001</v>
+      </c>
+      <c r="W18" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:22" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
+    <row r="19" spans="3:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:28" s="10" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:28" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="C22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T21" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="1" t="s">
+      <c r="U22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V21" s="1" t="s">
+      <c r="V22" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="X22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C22" s="1">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="C23" s="1">
         <v>0</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D23" s="2">
         <v>106</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2">
-        <v>165293</v>
-      </c>
-      <c r="G22" s="2">
-        <v>54056</v>
-      </c>
-      <c r="H22" s="2">
-        <v>3631</v>
-      </c>
-      <c r="I22" s="2">
-        <v>622.4778</v>
-      </c>
-      <c r="J22" s="2">
-        <v>10954</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1.1514999999999999E-2</v>
-      </c>
-      <c r="L22" s="2">
-        <v>6.7170999999999995E-2</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0.20264199999999999</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2">
-        <v>158372</v>
-      </c>
-      <c r="P22" s="2">
-        <v>49046</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>4086</v>
-      </c>
-      <c r="R22" s="2">
-        <v>666.41890000000001</v>
-      </c>
-      <c r="S22" s="2">
-        <v>4189</v>
-      </c>
-      <c r="T22" s="2">
-        <v>1.3587999999999999E-2</v>
-      </c>
-      <c r="U22" s="2">
-        <v>8.3309999999999995E-2</v>
-      </c>
-      <c r="V22" s="2">
-        <v>8.541E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>259</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F23" s="2">
-        <v>426039</v>
+        <v>165293</v>
       </c>
       <c r="G23" s="2">
-        <v>86579</v>
+        <v>54056</v>
       </c>
       <c r="H23" s="2">
-        <v>2061</v>
+        <v>3631</v>
       </c>
       <c r="I23" s="2">
-        <v>65.7166</v>
+        <v>622.4778</v>
       </c>
       <c r="J23" s="2">
-        <v>17942</v>
+        <v>10954</v>
       </c>
       <c r="K23" s="2">
-        <v>7.5900000000000002E-4</v>
+        <v>1.1514999999999999E-2</v>
       </c>
       <c r="L23" s="2">
-        <v>2.3805E-2</v>
+        <v>6.7170999999999995E-2</v>
       </c>
       <c r="M23" s="2">
-        <v>0.207233</v>
+        <v>0.20264199999999999</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O23" s="2">
-        <v>419206</v>
+        <v>158372</v>
       </c>
       <c r="P23" s="2">
-        <v>73133</v>
+        <v>49046</v>
       </c>
       <c r="Q23" s="2">
-        <v>2434</v>
+        <v>4086</v>
       </c>
       <c r="R23" s="2">
-        <v>73.2517</v>
+        <v>666.41890000000001</v>
       </c>
       <c r="S23" s="2">
-        <v>8151</v>
+        <v>4189</v>
       </c>
       <c r="T23" s="2">
-        <v>1.0020000000000001E-3</v>
+        <v>1.3587999999999999E-2</v>
       </c>
       <c r="U23" s="2">
-        <v>3.3281999999999999E-2</v>
+        <v>8.3309999999999995E-2</v>
       </c>
       <c r="V23" s="2">
-        <v>0.111454</v>
+        <v>8.541E-2</v>
+      </c>
+      <c r="X23" s="5">
+        <v>106</v>
+      </c>
+      <c r="Y23" s="14">
+        <f>F23/SUM($F$23:$F$26)</f>
+        <v>0.16403159701892447</v>
+      </c>
+      <c r="Z23" s="14">
+        <f>O23/SUM($O$23:$O$26)</f>
+        <v>0.16203877544965015</v>
+      </c>
+      <c r="AA23" s="14">
+        <f>I23/SUM($I$23:$I$26)</f>
+        <v>0.41445936159263536</v>
+      </c>
+      <c r="AB23" s="14">
+        <f>R23/SUM($R$23:$R$26)</f>
+        <v>0.39034677086240055</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>574</v>
+        <v>259</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>349233</v>
+        <v>426039</v>
       </c>
       <c r="G24" s="2">
-        <v>67583</v>
+        <v>86579</v>
       </c>
       <c r="H24" s="2">
-        <v>8277</v>
+        <v>2061</v>
       </c>
       <c r="I24" s="2">
-        <v>309.9486</v>
+        <v>65.7166</v>
       </c>
       <c r="J24" s="2">
-        <v>17527</v>
+        <v>17942</v>
       </c>
       <c r="K24" s="2">
-        <v>4.5859999999999998E-3</v>
+        <v>7.5900000000000002E-4</v>
       </c>
       <c r="L24" s="2">
-        <v>0.122472</v>
+        <v>2.3805E-2</v>
       </c>
       <c r="M24" s="2">
-        <v>0.25934000000000001</v>
+        <v>0.207233</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O24" s="2">
-        <v>337056</v>
+        <v>419206</v>
       </c>
       <c r="P24" s="2">
-        <v>59563</v>
+        <v>73133</v>
       </c>
       <c r="Q24" s="2">
-        <v>8722</v>
+        <v>2434</v>
       </c>
       <c r="R24" s="2">
-        <v>327.23200000000003</v>
+        <v>73.2517</v>
       </c>
       <c r="S24" s="2">
-        <v>9883</v>
+        <v>8151</v>
       </c>
       <c r="T24" s="2">
-        <v>5.4939999999999998E-3</v>
+        <v>1.0020000000000001E-3</v>
       </c>
       <c r="U24" s="2">
-        <v>0.14643300000000001</v>
+        <v>3.3281999999999999E-2</v>
       </c>
       <c r="V24" s="2">
-        <v>0.16592499999999999</v>
+        <v>0.111454</v>
+      </c>
+      <c r="X24" s="5">
+        <v>259</v>
+      </c>
+      <c r="Y24" s="14">
+        <f>F24/SUM($F$23:$F$26)</f>
+        <v>0.42278776210937885</v>
+      </c>
+      <c r="Z24" s="14">
+        <f>O24/SUM($O$23:$O$26)</f>
+        <v>0.42891184616691103</v>
+      </c>
+      <c r="AA24" s="14">
+        <f>I24/SUM($I$23:$I$26)</f>
+        <v>4.3755552538642474E-2</v>
+      </c>
+      <c r="AB24" s="14">
+        <f>R24/SUM($R$23:$R$26)</f>
+        <v>4.2906292956549262E-2</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>700</v>
+        <v>574</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F25" s="2">
-        <v>67125</v>
+        <v>349233</v>
       </c>
       <c r="G25" s="2">
-        <v>31834</v>
+        <v>67583</v>
       </c>
       <c r="H25" s="2">
-        <v>2063</v>
+        <v>8277</v>
       </c>
       <c r="I25" s="2">
-        <v>503.76010000000002</v>
+        <v>309.9486</v>
       </c>
       <c r="J25" s="2">
-        <v>6361</v>
+        <v>17527</v>
       </c>
       <c r="K25" s="2">
-        <v>1.5824999999999999E-2</v>
+        <v>4.5859999999999998E-3</v>
       </c>
       <c r="L25" s="2">
-        <v>6.4805000000000001E-2</v>
+        <v>0.122472</v>
       </c>
       <c r="M25" s="2">
-        <v>0.199818</v>
+        <v>0.25934000000000001</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O25" s="2">
+        <v>337056</v>
+      </c>
+      <c r="P25" s="2">
+        <v>59563</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>8722</v>
+      </c>
+      <c r="R25" s="2">
+        <v>327.23200000000003</v>
+      </c>
+      <c r="S25" s="2">
+        <v>9883</v>
+      </c>
+      <c r="T25" s="2">
+        <v>5.4939999999999998E-3</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0.14643300000000001</v>
+      </c>
+      <c r="V25" s="2">
+        <v>0.16592499999999999</v>
+      </c>
+      <c r="X25" s="5">
+        <v>574</v>
+      </c>
+      <c r="Y25" s="14">
+        <f>F25/SUM($F$23:$F$26)</f>
+        <v>0.34656789290357154</v>
+      </c>
+      <c r="Z25" s="14">
+        <f>O25/SUM($O$23:$O$26)</f>
+        <v>0.3448598331646836</v>
+      </c>
+      <c r="AA25" s="14">
+        <f>I25/SUM($I$23:$I$26)</f>
+        <v>0.20637057077783513</v>
+      </c>
+      <c r="AB25" s="14">
+        <f>R25/SUM($R$23:$R$26)</f>
+        <v>0.1916721667450384</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>700</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2">
+        <v>67125</v>
+      </c>
+      <c r="G26" s="2">
+        <v>31834</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2063</v>
+      </c>
+      <c r="I26" s="2">
+        <v>503.76010000000002</v>
+      </c>
+      <c r="J26" s="2">
+        <v>6361</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1.5824999999999999E-2</v>
+      </c>
+      <c r="L26" s="2">
+        <v>6.4805000000000001E-2</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0.199818</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2">
         <v>62737</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P26" s="2">
         <v>28852</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q26" s="2">
         <v>2401</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R26" s="2">
         <v>640.34580000000005</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S26" s="2">
         <v>2376</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T26" s="2">
         <v>2.2193999999999998E-2</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U26" s="2">
         <v>8.3218E-2</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V26" s="2">
         <v>8.2350999999999994E-2</v>
       </c>
+      <c r="X26" s="5">
+        <v>700</v>
+      </c>
+      <c r="Y26" s="14">
+        <f>F26/SUM($F$23:$F$26)</f>
+        <v>6.6612747968125122E-2</v>
+      </c>
+      <c r="Z26" s="14">
+        <f>O26/SUM($O$23:$O$26)</f>
+        <v>6.4189545218755209E-2</v>
+      </c>
+      <c r="AA26" s="14">
+        <f>I26/SUM($I$23:$I$26)</f>
+        <v>0.33541451509088704</v>
+      </c>
+      <c r="AB26" s="14">
+        <f>R26/SUM($R$23:$R$26)</f>
+        <v>0.37507476943601176</v>
+      </c>
     </row>
-    <row r="28" spans="3:22" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="E28" s="9" t="s">
+    <row r="29" spans="3:28" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I29" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K29" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="M29" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="O29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="E29" s="2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="E30" s="2">
         <v>106</v>
       </c>
-      <c r="F29" s="6">
-        <f t="shared" ref="F29:M32" si="1">O22-F22</f>
+      <c r="F30" s="6">
+        <f t="shared" ref="F30:M33" si="6">O23-F23</f>
         <v>-6921</v>
       </c>
-      <c r="G29" s="6">
-        <f t="shared" si="1"/>
+      <c r="G30" s="6">
+        <f t="shared" si="6"/>
         <v>-5010</v>
       </c>
-      <c r="H29" s="6">
-        <f t="shared" si="1"/>
+      <c r="H30" s="6">
+        <f t="shared" si="6"/>
         <v>455</v>
       </c>
-      <c r="I29" s="6">
-        <f t="shared" si="1"/>
+      <c r="I30" s="6">
+        <f t="shared" si="6"/>
         <v>43.941100000000006</v>
       </c>
-      <c r="J29" s="6">
-        <f t="shared" si="1"/>
+      <c r="J30" s="6">
+        <f t="shared" si="6"/>
         <v>-6765</v>
       </c>
-      <c r="K29" s="6">
-        <f t="shared" si="1"/>
+      <c r="K30" s="6">
+        <f t="shared" si="6"/>
         <v>2.0730000000000002E-3</v>
       </c>
-      <c r="L29" s="8">
-        <f t="shared" si="1"/>
+      <c r="L30" s="8">
+        <f t="shared" si="6"/>
         <v>1.6139000000000001E-2</v>
       </c>
-      <c r="M29" s="8">
-        <f t="shared" si="1"/>
+      <c r="M30" s="8">
+        <f t="shared" si="6"/>
         <v>-0.11723199999999999</v>
       </c>
+      <c r="O30" s="2">
+        <v>106</v>
+      </c>
+      <c r="P30" s="13">
+        <f>F23+O23</f>
+        <v>323665</v>
+      </c>
+      <c r="Q30" s="13">
+        <f t="shared" ref="Q30:T33" si="7">G23+P23</f>
+        <v>103102</v>
+      </c>
+      <c r="R30" s="13">
+        <f t="shared" si="7"/>
+        <v>7717</v>
+      </c>
+      <c r="S30" s="13">
+        <f t="shared" si="7"/>
+        <v>1288.8967</v>
+      </c>
+      <c r="T30" s="13">
+        <f t="shared" si="7"/>
+        <v>15143</v>
+      </c>
+      <c r="U30" s="6">
+        <f>S30/Q30*1000</f>
+        <v>12.50118038447363</v>
+      </c>
+      <c r="V30" s="8" t="e">
+        <f t="shared" ref="V30:V33" si="8">AE22-V22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W30" s="8">
+        <f t="shared" ref="W30:W33" si="9">AF22-W22</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="E30" s="2">
+    <row r="31" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="E31" s="2">
         <v>259</v>
       </c>
-      <c r="F30" s="6">
-        <f t="shared" si="1"/>
+      <c r="F31" s="6">
+        <f t="shared" si="6"/>
         <v>-6833</v>
       </c>
-      <c r="G30" s="6">
-        <f t="shared" si="1"/>
+      <c r="G31" s="6">
+        <f t="shared" si="6"/>
         <v>-13446</v>
       </c>
-      <c r="H30" s="6">
-        <f t="shared" si="1"/>
+      <c r="H31" s="6">
+        <f t="shared" si="6"/>
         <v>373</v>
       </c>
-      <c r="I30" s="6">
-        <f t="shared" si="1"/>
+      <c r="I31" s="6">
+        <f t="shared" si="6"/>
         <v>7.5350999999999999</v>
       </c>
-      <c r="J30" s="6">
-        <f t="shared" si="1"/>
+      <c r="J31" s="6">
+        <f t="shared" si="6"/>
         <v>-9791</v>
       </c>
-      <c r="K30" s="6">
-        <f t="shared" si="1"/>
+      <c r="K31" s="6">
+        <f t="shared" si="6"/>
         <v>2.4300000000000005E-4</v>
       </c>
-      <c r="L30" s="7">
-        <f t="shared" si="1"/>
+      <c r="L31" s="7">
+        <f t="shared" si="6"/>
         <v>9.4769999999999993E-3</v>
       </c>
-      <c r="M30" s="7">
-        <f t="shared" si="1"/>
+      <c r="M31" s="7">
+        <f t="shared" si="6"/>
         <v>-9.5779000000000003E-2</v>
       </c>
+      <c r="O31" s="2">
+        <v>259</v>
+      </c>
+      <c r="P31" s="13">
+        <f t="shared" ref="P31:P33" si="10">F24+O24</f>
+        <v>845245</v>
+      </c>
+      <c r="Q31" s="13">
+        <f t="shared" si="7"/>
+        <v>159712</v>
+      </c>
+      <c r="R31" s="13">
+        <f t="shared" si="7"/>
+        <v>4495</v>
+      </c>
+      <c r="S31" s="13">
+        <f t="shared" si="7"/>
+        <v>138.9683</v>
+      </c>
+      <c r="T31" s="13">
+        <f t="shared" si="7"/>
+        <v>26093</v>
+      </c>
+      <c r="U31" s="6">
+        <f t="shared" ref="U31:U33" si="11">S31/Q31*1000</f>
+        <v>0.87011808755760367</v>
+      </c>
+      <c r="V31" s="7">
+        <f t="shared" si="8"/>
+        <v>-8.541E-2</v>
+      </c>
+      <c r="W31" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="E31" s="2">
+    <row r="32" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="E32" s="2">
         <v>574</v>
       </c>
-      <c r="F31" s="6">
-        <f t="shared" si="1"/>
+      <c r="F32" s="6">
+        <f t="shared" si="6"/>
         <v>-12177</v>
       </c>
-      <c r="G31" s="6">
-        <f t="shared" si="1"/>
+      <c r="G32" s="6">
+        <f t="shared" si="6"/>
         <v>-8020</v>
       </c>
-      <c r="H31" s="6">
-        <f t="shared" si="1"/>
+      <c r="H32" s="6">
+        <f t="shared" si="6"/>
         <v>445</v>
       </c>
-      <c r="I31" s="6">
-        <f t="shared" si="1"/>
+      <c r="I32" s="6">
+        <f t="shared" si="6"/>
         <v>17.283400000000029</v>
       </c>
-      <c r="J31" s="6">
-        <f t="shared" si="1"/>
+      <c r="J32" s="6">
+        <f t="shared" si="6"/>
         <v>-7644</v>
       </c>
-      <c r="K31" s="6">
-        <f t="shared" si="1"/>
+      <c r="K32" s="6">
+        <f t="shared" si="6"/>
         <v>9.0799999999999995E-4</v>
       </c>
-      <c r="L31" s="7">
-        <f t="shared" si="1"/>
+      <c r="L32" s="7">
+        <f t="shared" si="6"/>
         <v>2.396100000000001E-2</v>
       </c>
-      <c r="M31" s="7">
-        <f t="shared" si="1"/>
+      <c r="M32" s="7">
+        <f t="shared" si="6"/>
         <v>-9.3415000000000026E-2</v>
       </c>
+      <c r="O32" s="2">
+        <v>574</v>
+      </c>
+      <c r="P32" s="13">
+        <f t="shared" si="10"/>
+        <v>686289</v>
+      </c>
+      <c r="Q32" s="13">
+        <f t="shared" si="7"/>
+        <v>127146</v>
+      </c>
+      <c r="R32" s="13">
+        <f t="shared" si="7"/>
+        <v>16999</v>
+      </c>
+      <c r="S32" s="13">
+        <f t="shared" si="7"/>
+        <v>637.18060000000003</v>
+      </c>
+      <c r="T32" s="13">
+        <f t="shared" si="7"/>
+        <v>27410</v>
+      </c>
+      <c r="U32" s="6">
+        <f t="shared" si="11"/>
+        <v>5.011408931464616</v>
+      </c>
+      <c r="V32" s="7">
+        <f t="shared" si="8"/>
+        <v>-0.111454</v>
+      </c>
+      <c r="W32" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="E32" s="2">
+    <row r="33" spans="5:23" x14ac:dyDescent="0.25">
+      <c r="E33" s="2">
         <v>700</v>
       </c>
-      <c r="F32" s="6">
-        <f t="shared" si="1"/>
+      <c r="F33" s="6">
+        <f t="shared" si="6"/>
         <v>-4388</v>
       </c>
-      <c r="G32" s="6">
-        <f t="shared" si="1"/>
+      <c r="G33" s="6">
+        <f t="shared" si="6"/>
         <v>-2982</v>
       </c>
-      <c r="H32" s="6">
-        <f t="shared" si="1"/>
+      <c r="H33" s="6">
+        <f t="shared" si="6"/>
         <v>338</v>
       </c>
-      <c r="I32" s="6">
-        <f t="shared" si="1"/>
+      <c r="I33" s="6">
+        <f t="shared" si="6"/>
         <v>136.58570000000003</v>
       </c>
-      <c r="J32" s="6">
-        <f t="shared" si="1"/>
+      <c r="J33" s="6">
+        <f t="shared" si="6"/>
         <v>-3985</v>
       </c>
-      <c r="K32" s="6">
-        <f t="shared" si="1"/>
+      <c r="K33" s="6">
+        <f t="shared" si="6"/>
         <v>6.3689999999999997E-3</v>
       </c>
-      <c r="L32" s="7">
-        <f t="shared" si="1"/>
+      <c r="L33" s="7">
+        <f t="shared" si="6"/>
         <v>1.8412999999999999E-2</v>
       </c>
-      <c r="M32" s="7">
-        <f t="shared" si="1"/>
+      <c r="M33" s="7">
+        <f t="shared" si="6"/>
         <v>-0.117467</v>
       </c>
+      <c r="O33" s="2">
+        <v>700</v>
+      </c>
+      <c r="P33" s="13">
+        <f t="shared" si="10"/>
+        <v>129862</v>
+      </c>
+      <c r="Q33" s="13">
+        <f t="shared" si="7"/>
+        <v>60686</v>
+      </c>
+      <c r="R33" s="13">
+        <f t="shared" si="7"/>
+        <v>4464</v>
+      </c>
+      <c r="S33" s="13">
+        <f t="shared" si="7"/>
+        <v>1144.1059</v>
+      </c>
+      <c r="T33" s="13">
+        <f t="shared" si="7"/>
+        <v>8737</v>
+      </c>
+      <c r="U33" s="6">
+        <f t="shared" si="11"/>
+        <v>18.85288040075141</v>
+      </c>
+      <c r="V33" s="7">
+        <f t="shared" si="8"/>
+        <v>-0.16592499999999999</v>
+      </c>
+      <c r="W33" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E33" s="2"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
+    <row r="34" spans="5:23" x14ac:dyDescent="0.25">
+      <c r="E34" s="2"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Table_temp.xlsx
+++ b/Table_temp.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="56">
   <si>
     <t>pageviews</t>
   </si>
@@ -125,18 +125,6 @@
     <t>B+A</t>
   </si>
   <si>
-    <t>pageviews_A, %</t>
-  </si>
-  <si>
-    <t>pageviews_В, %</t>
-  </si>
-  <si>
-    <t>revenue_А, %</t>
-  </si>
-  <si>
-    <t>revenue_В, %</t>
-  </si>
-  <si>
     <t>pageviews_A, % от тотал трафика</t>
   </si>
   <si>
@@ -147,6 +135,63 @@
   </si>
   <si>
     <t>revenue_В, % от тотал выручки</t>
+  </si>
+  <si>
+    <t>visible_pageviews_A % от тотал</t>
+  </si>
+  <si>
+    <t>visible_pageviews_В % от тотал</t>
+  </si>
+  <si>
+    <t>Visible/PageViews, A</t>
+  </si>
+  <si>
+    <t>Visible/PageViews, B</t>
+  </si>
+  <si>
+    <t>CPC,A</t>
+  </si>
+  <si>
+    <t>sponsord_clicks_A, % от тотал кликов</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Средневзвешенная выручка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднее за период </t>
+  </si>
+  <si>
+    <t>161.893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тренд (в день) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +7.4870</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +7.8762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ст. ошибка </t>
+  </si>
+  <si>
+    <t>167.348</t>
+  </si>
+  <si>
+    <t>1.34</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>А</t>
+  </si>
+  <si>
+    <t>В</t>
   </si>
 </sst>
 </file>
@@ -158,7 +203,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +255,13 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -225,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -263,13 +315,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -301,6 +416,36 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -583,16 +728,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C5:AB34"/>
+  <dimension ref="C5:AI55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" customWidth="1"/>
     <col min="16" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5703125" customWidth="1"/>
+    <col min="34" max="34" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:28" ht="51" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:35" ht="51" x14ac:dyDescent="0.25">
       <c r="C5" s="11" t="s">
         <v>30</v>
       </c>
@@ -657,19 +803,40 @@
         <v>9</v>
       </c>
       <c r="Y5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AB5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AC5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AF5" s="16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AG5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH5" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI5" s="20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>0</v>
       </c>
@@ -697,10 +864,10 @@
       <c r="K6" s="2">
         <v>6.1339999999999997E-3</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="15">
         <v>5.3839999999999999E-2</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="15">
         <v>0.166211</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -742,15 +909,39 @@
         <v>0.18367819897367985</v>
       </c>
       <c r="AA6" s="7">
+        <f>G6/SUM($G$6:$G$10)</f>
+        <v>0.1671055460017197</v>
+      </c>
+      <c r="AB6" s="7">
+        <f>P6/SUM($P$6:$P$10)</f>
+        <v>0.17495910827293204</v>
+      </c>
+      <c r="AC6" s="17">
         <f>I6/SUM($I$6:$I$10)</f>
         <v>0.21282147408486382</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AD6" s="7">
         <f>R6/SUM($R$6:$R$10)</f>
         <v>0.20960339641479586</v>
       </c>
-    </row>
-    <row r="7" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE6" s="14">
+        <f>G6/F6</f>
+        <v>0.3217334322026591</v>
+      </c>
+      <c r="AF6" s="14">
+        <f>P6/O6</f>
+        <v>0.30173035328046144</v>
+      </c>
+      <c r="AG6" s="19">
+        <f>H6/SUM($H$6:$H$10)</f>
+        <v>0.16752835223482321</v>
+      </c>
+      <c r="AH6" s="21">
+        <f>I6/H6</f>
+        <v>0.11393275261324042</v>
+      </c>
+    </row>
+    <row r="7" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1</v>
       </c>
@@ -778,10 +969,10 @@
       <c r="K7" s="2">
         <v>1.8710000000000001E-3</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="15">
         <v>6.2493E-2</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="15">
         <v>0.20807899999999999</v>
       </c>
       <c r="N7" s="2" t="s">
@@ -823,15 +1014,39 @@
         <v>0.16150471776195993</v>
       </c>
       <c r="AA7" s="7">
+        <f t="shared" ref="AA7:AA10" si="0">G7/SUM($G$6:$G$10)</f>
+        <v>0.33458727429062768</v>
+      </c>
+      <c r="AB7" s="7">
+        <f t="shared" ref="AB7:AB10" si="1">P7/SUM($P$6:$P$10)</f>
+        <v>0.34553901305922374</v>
+      </c>
+      <c r="AC7" s="17">
         <f>I7/SUM($I$6:$I$10)</f>
         <v>0.13000505994105477</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AD7" s="7">
         <f>R7/SUM($R$6:$R$10)</f>
         <v>0.12715930796827463</v>
       </c>
-    </row>
-    <row r="8" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE7" s="14">
+        <f t="shared" ref="AE7:AE10" si="2">G7/F7</f>
+        <v>0.6978321175382719</v>
+      </c>
+      <c r="AF7" s="14">
+        <f t="shared" ref="AF7:AF10" si="3">P7/O7</f>
+        <v>0.67772254394506226</v>
+      </c>
+      <c r="AG7" s="19">
+        <f t="shared" ref="AG7:AG10" si="4">H7/SUM($H$6:$H$10)</f>
+        <v>0.38934289526350901</v>
+      </c>
+      <c r="AH7" s="21">
+        <f t="shared" ref="AH7:AH10" si="5">I7/H7</f>
+        <v>2.994673377596916E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C8" s="1">
         <v>2</v>
       </c>
@@ -859,10 +1074,10 @@
       <c r="K8" s="2">
         <v>1.4153000000000001E-2</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="15">
         <v>6.6404000000000005E-2</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="15">
         <v>0.13240399999999999</v>
       </c>
       <c r="N8" s="2" t="s">
@@ -904,15 +1119,39 @@
         <v>0.14146995530541301</v>
       </c>
       <c r="AA8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.16678310404127258</v>
+      </c>
+      <c r="AB8" s="7">
+        <f t="shared" si="1"/>
+        <v>0.17464556148391244</v>
+      </c>
+      <c r="AC8" s="17">
         <f>I8/SUM($I$6:$I$10)</f>
         <v>0.49007965176596779</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AD8" s="7">
         <f>R8/SUM($R$6:$R$10)</f>
         <v>0.48988402953737642</v>
       </c>
-    </row>
-    <row r="9" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE8" s="14">
+        <f t="shared" si="2"/>
+        <v>0.41932578197131082</v>
+      </c>
+      <c r="AF8" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39105099342397792</v>
+      </c>
+      <c r="AG8" s="19">
+        <f t="shared" si="4"/>
+        <v>0.20622081387591729</v>
+      </c>
+      <c r="AH8" s="21">
+        <f t="shared" si="5"/>
+        <v>0.21313542256368781</v>
+      </c>
+    </row>
+    <row r="9" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C9" s="1">
         <v>3</v>
       </c>
@@ -940,10 +1179,10 @@
       <c r="K9" s="2">
         <v>3.0969999999999999E-3</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="15">
         <v>7.0805000000000007E-2</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="15">
         <v>0.17797199999999999</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -985,15 +1224,39 @@
         <v>0.24098659162390332</v>
       </c>
       <c r="AA9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10986314130123244</v>
+      </c>
+      <c r="AB9" s="7">
+        <f t="shared" si="1"/>
+        <v>0.12007796863486954</v>
+      </c>
+      <c r="AC9" s="17">
         <f>I9/SUM($I$6:$I$10)</f>
         <v>7.0634062124769859E-2</v>
       </c>
-      <c r="AB9" s="7">
+      <c r="AD9" s="7">
         <f>R9/SUM($R$6:$R$10)</f>
         <v>7.6748831848028304E-2</v>
       </c>
-    </row>
-    <row r="10" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE9" s="14">
+        <f t="shared" si="2"/>
+        <v>0.16550849401573317</v>
+      </c>
+      <c r="AF9" s="14">
+        <f t="shared" si="3"/>
+        <v>0.15783761505701333</v>
+      </c>
+      <c r="AG9" s="19">
+        <f t="shared" si="4"/>
+        <v>0.14484656437625085</v>
+      </c>
+      <c r="AH9" s="21">
+        <f t="shared" si="5"/>
+        <v>4.3734830166954515E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>4</v>
       </c>
@@ -1021,10 +1284,10 @@
       <c r="K10" s="2">
         <v>2.0960000000000002E-3</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="15">
         <v>2.2304999999999998E-2</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="15">
         <v>0.22991800000000001</v>
       </c>
       <c r="N10" s="2" t="s">
@@ -1066,15 +1329,39 @@
         <v>0.27236053633504387</v>
       </c>
       <c r="AA10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22166093436514761</v>
+      </c>
+      <c r="AB10" s="7">
+        <f t="shared" si="1"/>
+        <v>0.18477834854906222</v>
+      </c>
+      <c r="AC10" s="17">
         <f>I10/SUM($I$6:$I$10)</f>
         <v>9.64597520833438E-2</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AD10" s="7">
         <f>R10/SUM($R$6:$R$10)</f>
         <v>9.6604434231524816E-2</v>
       </c>
-    </row>
-    <row r="13" spans="3:28" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="AE10" s="14">
+        <f t="shared" si="2"/>
+        <v>0.28883040492043394</v>
+      </c>
+      <c r="AF10" s="14">
+        <f t="shared" si="3"/>
+        <v>0.21490521658269163</v>
+      </c>
+      <c r="AG10" s="19">
+        <f t="shared" si="4"/>
+        <v>9.2061374249499672E-2</v>
+      </c>
+      <c r="AH10" s="21">
+        <f t="shared" si="5"/>
+        <v>9.3970199275362321E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:35" ht="51" x14ac:dyDescent="0.25">
       <c r="E13" s="9" t="s">
         <v>29</v>
       </c>
@@ -1129,41 +1416,59 @@
       <c r="W13" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AB13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF13" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG13" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E14" s="5">
         <v>101</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" ref="F14:M18" si="0">O6-F6</f>
+        <f t="shared" ref="F14:M18" si="6">O6-F6</f>
         <v>-5018</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-3834</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-198</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-9.1723999999999819</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-2512</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.2900000000000056E-4</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>2.5200000000000222E-4</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-5.5996000000000004E-2</v>
       </c>
       <c r="O14" s="5">
@@ -1174,15 +1479,15 @@
         <v>226938</v>
       </c>
       <c r="Q14" s="13">
-        <f t="shared" ref="Q14:T18" si="1">G6+P6</f>
+        <f t="shared" ref="Q14:T18" si="7">G6+P6</f>
         <v>70794</v>
       </c>
       <c r="R14" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3820</v>
       </c>
       <c r="S14" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>448.60939999999999</v>
       </c>
       <c r="T14" s="13">
@@ -1194,305 +1499,395 @@
         <v>6.3368279797722966</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" ref="V14:V18" si="2">AE6-V6</f>
-        <v>-0.11021499999999999</v>
+        <f>R14/Q14</f>
+        <v>5.3959375088284321E-2</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" ref="W14:W18" si="3">AF6-W6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:28" x14ac:dyDescent="0.25">
+        <f>T14/Q14</f>
+        <v>0.13972935559510694</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>101</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>0.18367107772027289</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>0.1671055460017197</v>
+      </c>
+      <c r="AE14" s="17">
+        <v>0.21282147408486382</v>
+      </c>
+      <c r="AF14" s="19">
+        <v>0.16752835223482321</v>
+      </c>
+      <c r="AG14" s="21">
+        <v>0.11393275261324042</v>
+      </c>
+    </row>
+    <row r="15" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E15" s="5">
         <v>106</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-9498</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-8590</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-6.5254999999999939</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-8644</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.4499999999999995E-4</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>8.2849999999999938E-3</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-0.10369599999999998</v>
       </c>
       <c r="O15" s="5">
         <v>106</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15:P18" si="4">F7+O7</f>
+        <f t="shared" ref="P15:P18" si="8">F7+O7</f>
         <v>204628</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>140834</v>
       </c>
       <c r="R15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>9349</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>273.11710000000005</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>22448</v>
       </c>
       <c r="U15" s="6">
-        <f t="shared" ref="U15:U18" si="5">S15/Q15*1000</f>
+        <f t="shared" ref="U15:U18" si="9">S15/Q15*1000</f>
         <v>1.9392838377096442</v>
       </c>
-      <c r="V15" s="7">
-        <f t="shared" si="2"/>
-        <v>-0.104383</v>
-      </c>
-      <c r="W15" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="V15" s="8">
+        <f t="shared" ref="V15:V18" si="10">R15/Q15</f>
+        <v>6.6383117713052248E-2</v>
+      </c>
+      <c r="W15" s="8">
+        <f t="shared" ref="W15:W18" si="11">T15/Q15</f>
+        <v>0.1593933283156056</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>106</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>0.16955264441502335</v>
+      </c>
+      <c r="AD15" s="7">
+        <v>0.33458727429062768</v>
+      </c>
+      <c r="AE15" s="17">
+        <v>0.13000505994105477</v>
+      </c>
+      <c r="AF15" s="19">
+        <v>0.38934289526350901</v>
+      </c>
+      <c r="AG15" s="21">
+        <v>2.994673377596916E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E16" s="5">
         <v>111</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-3352</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-3822</v>
       </c>
       <c r="H16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-87</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-13.558899999999994</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-3318</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.2129999999999988E-3</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.9899999999999944E-3</v>
       </c>
       <c r="M16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-8.4138999999999992E-2</v>
       </c>
       <c r="O16" s="5">
         <v>111</v>
       </c>
       <c r="P16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>174276</v>
       </c>
       <c r="Q16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>70662</v>
       </c>
       <c r="R16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>4859</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1040.6088999999999</v>
       </c>
       <c r="T16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>6544</v>
       </c>
       <c r="U16" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>14.726570150859018</v>
       </c>
-      <c r="V16" s="7">
-        <f t="shared" si="2"/>
-        <v>-4.8265000000000002E-2</v>
-      </c>
-      <c r="W16" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="V16" s="8">
+        <f t="shared" si="10"/>
+        <v>6.8763974979479781E-2</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" si="11"/>
+        <v>9.2609889332314399E-2</v>
+      </c>
+      <c r="AB16" s="5">
+        <v>111</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>0.14065221935753605</v>
+      </c>
+      <c r="AD16" s="7">
+        <v>0.16678310404127258</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0.49007965176596779</v>
+      </c>
+      <c r="AF16" s="19">
+        <v>0.20622081387591729</v>
+      </c>
+      <c r="AG16" s="21">
+        <v>0.21313542256368781</v>
+      </c>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E17" s="5">
         <v>123</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-2642</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-1554</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>156</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.4852000000000061</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-2197</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.0400000000000028E-4</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.1577999999999991E-2</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-8.3576999999999985E-2</v>
       </c>
       <c r="O17" s="5">
         <v>123</v>
       </c>
       <c r="P17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>293802</v>
       </c>
       <c r="Q17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>47510</v>
       </c>
       <c r="R17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3630</v>
       </c>
       <c r="S17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>156.42000000000002</v>
       </c>
       <c r="T17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>6535</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3.2923595032624715</v>
       </c>
-      <c r="V17" s="7">
-        <f t="shared" si="2"/>
-        <v>-9.4395000000000007E-2</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="V17" s="8">
+        <f t="shared" si="10"/>
+        <v>7.6404967375289415E-2</v>
+      </c>
+      <c r="W17" s="8">
+        <f t="shared" si="11"/>
+        <v>0.1375499894758998</v>
+      </c>
+      <c r="AB17" s="5">
+        <v>123</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>0.23473498837584963</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>0.10986314130123244</v>
+      </c>
+      <c r="AE17" s="17">
+        <v>7.0634062124769859E-2</v>
+      </c>
+      <c r="AF17" s="19">
+        <v>0.14484656437625085</v>
+      </c>
+      <c r="AG17" s="21">
+        <v>4.3734830166954515E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E18" s="5">
         <v>373</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-6834</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-14137</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-2.4766999999999939</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-6691</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>7.6799999999999959E-4</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.0077000000000003E-2</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>-9.7307000000000005E-2</v>
       </c>
       <c r="O18" s="5">
         <v>373</v>
       </c>
       <c r="P18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>335900</v>
       </c>
       <c r="Q18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>84855</v>
       </c>
       <c r="R18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>2249</v>
       </c>
       <c r="S18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>205.0095</v>
       </c>
       <c r="T18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>16069</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4159978787343115</v>
       </c>
-      <c r="V18" s="7">
-        <f t="shared" si="2"/>
-        <v>-0.13261100000000001</v>
-      </c>
-      <c r="W18" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:28" s="10" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:28" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="V18" s="8">
+        <f t="shared" si="10"/>
+        <v>2.6504036297212891E-2</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" si="11"/>
+        <v>0.18937010193860115</v>
+      </c>
+      <c r="AB18" s="5">
+        <v>373</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>0.27138907013131808</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>0.22166093436514761</v>
+      </c>
+      <c r="AE18" s="17">
+        <v>9.64597520833438E-2</v>
+      </c>
+      <c r="AF18" s="19">
+        <v>9.2061374249499672E-2</v>
+      </c>
+      <c r="AG18" s="21">
+        <v>9.3970199275362321E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:35" s="10" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:35" ht="51" x14ac:dyDescent="0.25">
       <c r="C22" s="12" t="s">
         <v>31</v>
       </c>
@@ -1562,14 +1957,35 @@
       <c r="Z22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AA22" s="4" t="s">
+      <c r="AA22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB22" s="4" t="s">
+      <c r="AD22" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF22" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH22" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI22" s="20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C23" s="1">
         <v>0</v>
       </c>
@@ -1597,10 +2013,10 @@
       <c r="K23" s="2">
         <v>1.1514999999999999E-2</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="15">
         <v>6.7170999999999995E-2</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="15">
         <v>0.20264199999999999</v>
       </c>
       <c r="N23" s="2" t="s">
@@ -1624,10 +2040,10 @@
       <c r="T23" s="2">
         <v>1.3587999999999999E-2</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="15">
         <v>8.3309999999999995E-2</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" s="15">
         <v>8.541E-2</v>
       </c>
       <c r="X23" s="5">
@@ -1641,16 +2057,40 @@
         <f>O23/SUM($O$23:$O$26)</f>
         <v>0.16203877544965015</v>
       </c>
-      <c r="AA23" s="14">
+      <c r="AA23" s="7">
+        <f>G23/SUM($G$23:$G$26)</f>
+        <v>0.22518454334894106</v>
+      </c>
+      <c r="AB23" s="7">
+        <f>P23/SUM($P$23:$P$26)</f>
+        <v>0.23289362469965905</v>
+      </c>
+      <c r="AC23" s="17">
         <f>I23/SUM($I$23:$I$26)</f>
         <v>0.41445936159263536</v>
       </c>
-      <c r="AB23" s="14">
+      <c r="AD23" s="7">
         <f>R23/SUM($R$23:$R$26)</f>
         <v>0.39034677086240055</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE23" s="14">
+        <f>G23/F23</f>
+        <v>0.32703139273895449</v>
+      </c>
+      <c r="AF23" s="14">
+        <f>P23/O23</f>
+        <v>0.30968858131487892</v>
+      </c>
+      <c r="AG23" s="19">
+        <f>H23/SUM($H$23:$H$26)</f>
+        <v>0.22648453093812376</v>
+      </c>
+      <c r="AH23" s="21">
+        <f>I23/H23</f>
+        <v>0.17143426053428806</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C24" s="1">
         <v>1</v>
       </c>
@@ -1678,10 +2118,10 @@
       <c r="K24" s="2">
         <v>7.5900000000000002E-4</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="15">
         <v>2.3805E-2</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="15">
         <v>0.207233</v>
       </c>
       <c r="N24" s="2" t="s">
@@ -1705,10 +2145,10 @@
       <c r="T24" s="2">
         <v>1.0020000000000001E-3</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="15">
         <v>3.3281999999999999E-2</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="15">
         <v>0.111454</v>
       </c>
       <c r="X24" s="5">
@@ -1722,16 +2162,40 @@
         <f>O24/SUM($O$23:$O$26)</f>
         <v>0.42891184616691103</v>
       </c>
-      <c r="AA24" s="14">
-        <f>I24/SUM($I$23:$I$26)</f>
+      <c r="AA24" s="7">
+        <f t="shared" ref="AA24:AA26" si="12">G24/SUM($G$23:$G$26)</f>
+        <v>0.36066768866745541</v>
+      </c>
+      <c r="AB24" s="7">
+        <f t="shared" ref="AB24:AB26" si="13">P24/SUM($P$23:$P$26)</f>
+        <v>0.34727010266199415</v>
+      </c>
+      <c r="AC24" s="17">
+        <f t="shared" ref="AC24:AC26" si="14">I24/SUM($I$23:$I$26)</f>
         <v>4.3755552538642474E-2</v>
       </c>
-      <c r="AB24" s="14">
-        <f>R24/SUM($R$23:$R$26)</f>
+      <c r="AD24" s="7">
+        <f t="shared" ref="AD24:AD26" si="15">R24/SUM($R$23:$R$26)</f>
         <v>4.2906292956549262E-2</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE24" s="14">
+        <f t="shared" ref="AE24:AE26" si="16">G24/F24</f>
+        <v>0.20321848469271592</v>
+      </c>
+      <c r="AF24" s="14">
+        <f t="shared" ref="AF24:AF26" si="17">P24/O24</f>
+        <v>0.1744559953817455</v>
+      </c>
+      <c r="AG24" s="19">
+        <f t="shared" ref="AG24:AG26" si="18">H24/SUM($H$23:$H$26)</f>
+        <v>0.12855538922155688</v>
+      </c>
+      <c r="AH24" s="21">
+        <f t="shared" ref="AH24:AH26" si="19">I24/H24</f>
+        <v>3.1885783600194083E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C25" s="1">
         <v>2</v>
       </c>
@@ -1759,10 +2223,10 @@
       <c r="K25" s="2">
         <v>4.5859999999999998E-3</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="15">
         <v>0.122472</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="15">
         <v>0.25934000000000001</v>
       </c>
       <c r="N25" s="2" t="s">
@@ -1786,10 +2250,10 @@
       <c r="T25" s="2">
         <v>5.4939999999999998E-3</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="15">
         <v>0.14643300000000001</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V25" s="15">
         <v>0.16592499999999999</v>
       </c>
       <c r="X25" s="5">
@@ -1803,16 +2267,40 @@
         <f>O25/SUM($O$23:$O$26)</f>
         <v>0.3448598331646836</v>
       </c>
-      <c r="AA25" s="14">
-        <f>I25/SUM($I$23:$I$26)</f>
+      <c r="AA25" s="7">
+        <f t="shared" si="12"/>
+        <v>0.28153483411927416</v>
+      </c>
+      <c r="AB25" s="7">
+        <f t="shared" si="13"/>
+        <v>0.28283331908791326</v>
+      </c>
+      <c r="AC25" s="17">
+        <f t="shared" si="14"/>
         <v>0.20637057077783513</v>
       </c>
-      <c r="AB25" s="14">
-        <f>R25/SUM($R$23:$R$26)</f>
+      <c r="AD25" s="7">
+        <f t="shared" si="15"/>
         <v>0.1916721667450384</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AE25" s="14">
+        <f t="shared" si="16"/>
+        <v>0.19351836739368847</v>
+      </c>
+      <c r="AF25" s="14">
+        <f t="shared" si="17"/>
+        <v>0.17671544194436534</v>
+      </c>
+      <c r="AG25" s="19">
+        <f t="shared" si="18"/>
+        <v>0.51627994011976053</v>
+      </c>
+      <c r="AH25" s="21">
+        <f t="shared" si="19"/>
+        <v>3.7446973541138094E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C26" s="1">
         <v>3</v>
       </c>
@@ -1840,10 +2328,10 @@
       <c r="K26" s="2">
         <v>1.5824999999999999E-2</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="15">
         <v>6.4805000000000001E-2</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="15">
         <v>0.199818</v>
       </c>
       <c r="N26" s="2" t="s">
@@ -1867,10 +2355,10 @@
       <c r="T26" s="2">
         <v>2.2193999999999998E-2</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="15">
         <v>8.3218E-2</v>
       </c>
-      <c r="V26" s="2">
+      <c r="V26" s="15">
         <v>8.2350999999999994E-2</v>
       </c>
       <c r="X26" s="5">
@@ -1884,16 +2372,40 @@
         <f>O26/SUM($O$23:$O$26)</f>
         <v>6.4189545218755209E-2</v>
       </c>
-      <c r="AA26" s="14">
-        <f>I26/SUM($I$23:$I$26)</f>
+      <c r="AA26" s="7">
+        <f t="shared" si="12"/>
+        <v>0.1326129338643294</v>
+      </c>
+      <c r="AB26" s="7">
+        <f t="shared" si="13"/>
+        <v>0.13700295355043354</v>
+      </c>
+      <c r="AC26" s="17">
+        <f t="shared" si="14"/>
         <v>0.33541451509088704</v>
       </c>
-      <c r="AB26" s="14">
-        <f>R26/SUM($R$23:$R$26)</f>
+      <c r="AD26" s="7">
+        <f t="shared" si="15"/>
         <v>0.37507476943601176</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="AE26" s="14">
+        <f t="shared" si="16"/>
+        <v>0.47424953445065177</v>
+      </c>
+      <c r="AF26" s="14">
+        <f t="shared" si="17"/>
+        <v>0.45988810430846233</v>
+      </c>
+      <c r="AG26" s="19">
+        <f t="shared" si="18"/>
+        <v>0.12868013972055889</v>
+      </c>
+      <c r="AH26" s="21">
+        <f t="shared" si="19"/>
+        <v>0.24418812409112944</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" ht="51" x14ac:dyDescent="0.25">
       <c r="E29" s="9" t="s">
         <v>29</v>
       </c>
@@ -1948,41 +2460,59 @@
       <c r="W29" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="AB29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF29" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG29" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E30" s="2">
         <v>106</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" ref="F30:M33" si="6">O23-F23</f>
+        <f t="shared" ref="F30:M33" si="20">O23-F23</f>
         <v>-6921</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-5010</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>455</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>43.941100000000006</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-6765</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>2.0730000000000002E-3</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>1.6139000000000001E-2</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-0.11723199999999999</v>
       </c>
       <c r="O30" s="2">
@@ -1993,251 +2523,323 @@
         <v>323665</v>
       </c>
       <c r="Q30" s="13">
-        <f t="shared" ref="Q30:T33" si="7">G23+P23</f>
+        <f t="shared" ref="Q30:T33" si="21">G23+P23</f>
         <v>103102</v>
       </c>
       <c r="R30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>7717</v>
       </c>
       <c r="S30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>1288.8967</v>
       </c>
       <c r="T30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>15143</v>
       </c>
       <c r="U30" s="6">
         <f>S30/Q30*1000</f>
         <v>12.50118038447363</v>
       </c>
-      <c r="V30" s="8" t="e">
-        <f t="shared" ref="V30:V33" si="8">AE22-V22</f>
-        <v>#VALUE!</v>
+      <c r="V30" s="8">
+        <f>R30/Q30</f>
+        <v>7.4848208570153826E-2</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" ref="W30:W33" si="9">AF22-W22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.25">
+        <f>T30/Q30</f>
+        <v>0.14687396946712963</v>
+      </c>
+      <c r="AB30" s="5">
+        <v>106</v>
+      </c>
+      <c r="AC30" s="14">
+        <v>0.16403159701892447</v>
+      </c>
+      <c r="AD30" s="7">
+        <v>0.22518454334894106</v>
+      </c>
+      <c r="AE30" s="17">
+        <v>0.41445936159263536</v>
+      </c>
+      <c r="AF30" s="19">
+        <v>0.22648453093812376</v>
+      </c>
+      <c r="AG30" s="21">
+        <v>0.17143426053428806</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E31" s="2">
         <v>259</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-6833</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-13446</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>373</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>7.5350999999999999</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-9791</v>
       </c>
       <c r="K31" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>2.4300000000000005E-4</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>9.4769999999999993E-3</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-9.5779000000000003E-2</v>
       </c>
       <c r="O31" s="2">
         <v>259</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" ref="P31:P33" si="10">F24+O24</f>
+        <f t="shared" ref="P31:P33" si="22">F24+O24</f>
         <v>845245</v>
       </c>
       <c r="Q31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>159712</v>
       </c>
       <c r="R31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>4495</v>
       </c>
       <c r="S31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>138.9683</v>
       </c>
       <c r="T31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>26093</v>
       </c>
       <c r="U31" s="6">
-        <f t="shared" ref="U31:U33" si="11">S31/Q31*1000</f>
+        <f t="shared" ref="U31:U33" si="23">S31/Q31*1000</f>
         <v>0.87011808755760367</v>
       </c>
-      <c r="V31" s="7">
-        <f t="shared" si="8"/>
-        <v>-8.541E-2</v>
-      </c>
-      <c r="W31" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="V31" s="8">
+        <f t="shared" ref="V31:V33" si="24">R31/Q31</f>
+        <v>2.81444099378882E-2</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" ref="W31:W33" si="25">T31/Q31</f>
+        <v>0.16337532558605489</v>
+      </c>
+      <c r="AB31" s="5">
+        <v>259</v>
+      </c>
+      <c r="AC31" s="14">
+        <v>0.42278776210937885</v>
+      </c>
+      <c r="AD31" s="7">
+        <v>0.36066768866745541</v>
+      </c>
+      <c r="AE31" s="17">
+        <v>4.3755552538642474E-2</v>
+      </c>
+      <c r="AF31" s="19">
+        <v>0.12855538922155688</v>
+      </c>
+      <c r="AG31" s="21">
+        <v>3.1885783600194083E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.25">
       <c r="E32" s="2">
         <v>574</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-12177</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-8020</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>445</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>17.283400000000029</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-7644</v>
       </c>
       <c r="K32" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>9.0799999999999995E-4</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>2.396100000000001E-2</v>
       </c>
       <c r="M32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-9.3415000000000026E-2</v>
       </c>
       <c r="O32" s="2">
         <v>574</v>
       </c>
       <c r="P32" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>686289</v>
       </c>
       <c r="Q32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>127146</v>
       </c>
       <c r="R32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>16999</v>
       </c>
       <c r="S32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>637.18060000000003</v>
       </c>
       <c r="T32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>27410</v>
       </c>
       <c r="U32" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>5.011408931464616</v>
       </c>
-      <c r="V32" s="7">
-        <f t="shared" si="8"/>
-        <v>-0.111454</v>
-      </c>
-      <c r="W32" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="5:23" x14ac:dyDescent="0.25">
+      <c r="V32" s="8">
+        <f t="shared" si="24"/>
+        <v>0.133696695137873</v>
+      </c>
+      <c r="W32" s="8">
+        <f t="shared" si="25"/>
+        <v>0.21557894074528494</v>
+      </c>
+      <c r="AB32" s="5">
+        <v>574</v>
+      </c>
+      <c r="AC32" s="14">
+        <v>0.34656789290357154</v>
+      </c>
+      <c r="AD32" s="7">
+        <v>0.28153483411927416</v>
+      </c>
+      <c r="AE32" s="17">
+        <v>0.20637057077783513</v>
+      </c>
+      <c r="AF32" s="19">
+        <v>0.51627994011976053</v>
+      </c>
+      <c r="AG32" s="21">
+        <v>3.7446973541138094E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E33" s="2">
         <v>700</v>
       </c>
       <c r="F33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-4388</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-2982</v>
       </c>
       <c r="H33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>338</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>136.58570000000003</v>
       </c>
       <c r="J33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-3985</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>6.3689999999999997E-3</v>
       </c>
       <c r="L33" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>1.8412999999999999E-2</v>
       </c>
       <c r="M33" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-0.117467</v>
       </c>
       <c r="O33" s="2">
         <v>700</v>
       </c>
       <c r="P33" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>129862</v>
       </c>
       <c r="Q33" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>60686</v>
       </c>
       <c r="R33" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>4464</v>
       </c>
       <c r="S33" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>1144.1059</v>
       </c>
       <c r="T33" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>8737</v>
       </c>
       <c r="U33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>18.85288040075141</v>
       </c>
-      <c r="V33" s="7">
-        <f t="shared" si="8"/>
-        <v>-0.16592499999999999</v>
-      </c>
-      <c r="W33" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="5:23" x14ac:dyDescent="0.25">
+      <c r="V33" s="8">
+        <f t="shared" si="24"/>
+        <v>7.3558975711037144E-2</v>
+      </c>
+      <c r="W33" s="8">
+        <f t="shared" si="25"/>
+        <v>0.14397060277493987</v>
+      </c>
+      <c r="AB33" s="5">
+        <v>700</v>
+      </c>
+      <c r="AC33" s="14">
+        <v>6.6612747968125122E-2</v>
+      </c>
+      <c r="AD33" s="7">
+        <v>0.1326129338643294</v>
+      </c>
+      <c r="AE33" s="17">
+        <v>0.33541451509088704</v>
+      </c>
+      <c r="AF33" s="19">
+        <v>0.12868013972055889</v>
+      </c>
+      <c r="AG33" s="21">
+        <v>0.24418812409112944</v>
+      </c>
+    </row>
+    <row r="34" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E34" s="2"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -2257,7 +2859,204 @@
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
     </row>
+    <row r="39" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I39" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="25"/>
+      <c r="K39" s="26"/>
+      <c r="N39" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="O39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I40" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="K40" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="M40" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="N40" t="s">
+        <v>51</v>
+      </c>
+      <c r="O40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I41" s="6">
+        <v>1</v>
+      </c>
+      <c r="J41" s="21">
+        <v>149.44759999999999</v>
+      </c>
+      <c r="K41" s="21">
+        <v>142.91460000000001</v>
+      </c>
+      <c r="M41" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41" t="s">
+        <v>48</v>
+      </c>
+      <c r="O41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I42" s="6">
+        <v>2</v>
+      </c>
+      <c r="J42" s="21">
+        <v>151.913239</v>
+      </c>
+      <c r="K42" s="21">
+        <v>150.75843399999999</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="O42" s="28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I43" s="6">
+        <v>3</v>
+      </c>
+      <c r="J43" s="21">
+        <v>161.477003</v>
+      </c>
+      <c r="K43" s="21">
+        <v>150.71530300000001</v>
+      </c>
+    </row>
+    <row r="44" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I44" s="6">
+        <v>4</v>
+      </c>
+      <c r="J44" s="21">
+        <v>180.14837700000001</v>
+      </c>
+      <c r="K44" s="21">
+        <v>172.277602</v>
+      </c>
+    </row>
+    <row r="45" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I45" s="6">
+        <v>5</v>
+      </c>
+      <c r="J45" s="21">
+        <v>179.57375400000001</v>
+      </c>
+      <c r="K45" s="21">
+        <v>176.24748299999999</v>
+      </c>
+    </row>
+    <row r="46" spans="5:33" x14ac:dyDescent="0.25">
+      <c r="I46" s="6">
+        <v>6</v>
+      </c>
+      <c r="J46" s="21">
+        <v>181.526141</v>
+      </c>
+      <c r="K46" s="21">
+        <v>178.44220000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I49" t="s">
+        <v>43</v>
+      </c>
+      <c r="J49" t="s">
+        <v>7</v>
+      </c>
+      <c r="K49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" s="22">
+        <v>214.11840000000001</v>
+      </c>
+      <c r="K50" s="22">
+        <v>251.63319999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51" s="22">
+        <v>214.24442099999999</v>
+      </c>
+      <c r="K51" s="22">
+        <v>251.800847</v>
+      </c>
+    </row>
+    <row r="52" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52" s="22">
+        <v>221.12867199999999</v>
+      </c>
+      <c r="K52" s="22">
+        <v>261.20667099999997</v>
+      </c>
+    </row>
+    <row r="53" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53" s="22">
+        <v>234.616761</v>
+      </c>
+      <c r="K53" s="22">
+        <v>268.04858999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54" s="22">
+        <v>257.55510399999997</v>
+      </c>
+      <c r="K54" s="22">
+        <v>288.21780999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I55">
+        <v>6</v>
+      </c>
+      <c r="J55" s="22">
+        <v>250.95469399999999</v>
+      </c>
+      <c r="K55" s="22">
+        <v>284.86551600000001</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I39:K39"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
